--- a/Active Loan Template.xlsx
+++ b/Active Loan Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://redwoodtrust-my.sharepoint.com/personal/jonathan_smith_cvest_com/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38EFFED4-85DC-432A-B13F-ADCAD01BF0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{38EFFED4-85DC-432A-B13F-ADCAD01BF0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74DBB7C4-A046-4C3F-9CA2-193081B4A44F}"/>
   <bookViews>
-    <workbookView xWindow="12255" yWindow="-16485" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00C131C7-9DB3-4C4E-AD78-2CBF562B522A}"/>
+    <workbookView xWindow="12255" yWindow="-16485" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00C131C7-9DB3-4C4E-AD78-2CBF562B522A}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="15" r:id="rId1"/>
@@ -4713,9 +4713,9 @@
       </c>
     </row>
     <row r="3" spans="2:30" x14ac:dyDescent="0.35">
-      <c r="P3" s="16" t="e">
-        <f>SUBTOTAL(9,#REF!)</f>
-        <v>#REF!</v>
+      <c r="P3" s="16">
+        <f>SUBTOTAL(9,P5:P5)</f>
+        <v>0</v>
       </c>
       <c r="U3" s="50">
         <v>46157</v>

--- a/Active Loan Template.xlsx
+++ b/Active Loan Template.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="7" documentId="8_{38EFFED4-85DC-432A-B13F-ADCAD01BF0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75A95C5A-0645-4695-AC46-9B0956BDA4F8}"/>
   <bookViews>
-    <workbookView xWindow="-16545" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00C131C7-9DB3-4C4E-AD78-2CBF562B522A}"/>
+    <workbookView xWindow="-16545" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00C131C7-9DB3-4C4E-AD78-2CBF562B522A}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="15" r:id="rId1"/>

--- a/Active Loan Template.xlsx
+++ b/Active Loan Template.xlsx
@@ -12,7 +12,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bridge Asset" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Term Loan" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Term Asset" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pacific Life" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SSP Loans" sheetId="8" state="hidden" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy" sheetId="9" state="hidden" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategy Groupings" sheetId="10" state="hidden" r:id="rId10"/>
@@ -7421,838 +7420,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:CH3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
-  <cols>
-    <col width="11.81640625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="10.453125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="16.26953125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="15" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="14.54296875" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="29" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="20.26953125" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="19.1796875" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="43" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="16.7265625" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="12.54296875" bestFit="1" customWidth="1" min="11" max="11"/>
-    <col width="13.81640625" bestFit="1" customWidth="1" min="12" max="12"/>
-    <col width="12.1796875" bestFit="1" customWidth="1" min="13" max="13"/>
-    <col width="13.26953125" bestFit="1" customWidth="1" min="14" max="15"/>
-    <col width="26.453125" bestFit="1" customWidth="1" min="16" max="16"/>
-    <col width="4" bestFit="1" customWidth="1" min="17" max="17"/>
-    <col width="15.81640625" bestFit="1" customWidth="1" min="18" max="18"/>
-    <col width="15.453125" bestFit="1" customWidth="1" min="19" max="19"/>
-    <col width="15.1796875" bestFit="1" customWidth="1" min="20" max="20"/>
-    <col width="9.453125" bestFit="1" customWidth="1" min="21" max="21"/>
-    <col width="12.26953125" bestFit="1" customWidth="1" min="22" max="23"/>
-    <col width="15.453125" bestFit="1" customWidth="1" min="24" max="24"/>
-    <col width="14" bestFit="1" customWidth="1" min="25" max="25"/>
-    <col width="12.81640625" bestFit="1" customWidth="1" min="26" max="26"/>
-    <col width="19.26953125" bestFit="1" customWidth="1" min="27" max="27"/>
-    <col width="14.54296875" bestFit="1" customWidth="1" min="28" max="28"/>
-    <col width="15" bestFit="1" customWidth="1" min="29" max="29"/>
-    <col width="14.54296875" bestFit="1" customWidth="1" min="30" max="30"/>
-    <col width="15.81640625" bestFit="1" customWidth="1" min="31" max="31"/>
-    <col width="10.7265625" bestFit="1" customWidth="1" min="32" max="32"/>
-    <col width="10.81640625" bestFit="1" customWidth="1" min="33" max="33"/>
-    <col width="20.26953125" bestFit="1" customWidth="1" min="34" max="34"/>
-    <col width="13.26953125" bestFit="1" customWidth="1" min="35" max="35"/>
-    <col width="12" bestFit="1" customWidth="1" min="36" max="36"/>
-    <col width="14" bestFit="1" customWidth="1" min="37" max="37"/>
-    <col width="13.26953125" bestFit="1" customWidth="1" min="38" max="38"/>
-    <col width="12.54296875" bestFit="1" customWidth="1" min="39" max="39"/>
-    <col width="12.453125" bestFit="1" customWidth="1" min="40" max="40"/>
-    <col width="13.81640625" bestFit="1" customWidth="1" min="41" max="41"/>
-    <col width="15.54296875" bestFit="1" customWidth="1" min="42" max="42"/>
-    <col width="12.81640625" bestFit="1" customWidth="1" min="43" max="43"/>
-    <col width="9.453125" bestFit="1" customWidth="1" min="44" max="44"/>
-    <col width="10" bestFit="1" customWidth="1" min="45" max="45"/>
-    <col width="8.453125" bestFit="1" customWidth="1" min="46" max="46"/>
-    <col width="10.7265625" bestFit="1" customWidth="1" min="47" max="47"/>
-    <col width="11.7265625" bestFit="1" customWidth="1" min="48" max="48"/>
-    <col width="9.7265625" bestFit="1" customWidth="1" min="49" max="49"/>
-    <col width="7.1796875" bestFit="1" customWidth="1" min="50" max="50"/>
-    <col width="10.81640625" bestFit="1" customWidth="1" min="51" max="51"/>
-    <col width="21.453125" bestFit="1" customWidth="1" min="52" max="52"/>
-    <col width="10.453125" bestFit="1" customWidth="1" min="53" max="53"/>
-    <col width="9.81640625" bestFit="1" customWidth="1" min="54" max="54"/>
-    <col width="24.81640625" bestFit="1" customWidth="1" min="55" max="55"/>
-    <col width="22.7265625" bestFit="1" customWidth="1" min="56" max="56"/>
-    <col width="27.453125" bestFit="1" customWidth="1" min="57" max="57"/>
-    <col width="28.1796875" bestFit="1" customWidth="1" min="58" max="58"/>
-    <col width="15.7265625" bestFit="1" customWidth="1" min="59" max="59"/>
-    <col width="19.1796875" bestFit="1" customWidth="1" min="60" max="60"/>
-    <col width="9.26953125" bestFit="1" customWidth="1" min="61" max="61"/>
-    <col width="21.81640625" bestFit="1" customWidth="1" min="62" max="62"/>
-    <col width="11.453125" bestFit="1" customWidth="1" min="63" max="63"/>
-    <col width="15.453125" bestFit="1" customWidth="1" min="64" max="64"/>
-    <col width="14.81640625" bestFit="1" customWidth="1" min="65" max="65"/>
-    <col width="15" bestFit="1" customWidth="1" min="66" max="66"/>
-    <col width="16.81640625" bestFit="1" customWidth="1" min="67" max="67"/>
-    <col width="42.1796875" bestFit="1" customWidth="1" min="68" max="68"/>
-    <col width="11.26953125" bestFit="1" customWidth="1" min="69" max="69"/>
-    <col width="17.54296875" bestFit="1" customWidth="1" min="70" max="70"/>
-    <col width="18.81640625" bestFit="1" customWidth="1" min="71" max="71"/>
-    <col width="11.453125" bestFit="1" customWidth="1" min="72" max="72"/>
-    <col width="14.1796875" bestFit="1" customWidth="1" min="73" max="73"/>
-    <col width="26.26953125" bestFit="1" customWidth="1" min="74" max="74"/>
-    <col width="15" bestFit="1" customWidth="1" min="75" max="75"/>
-    <col width="15.453125" bestFit="1" customWidth="1" min="76" max="76"/>
-    <col width="25.54296875" bestFit="1" customWidth="1" min="77" max="77"/>
-    <col width="13.26953125" bestFit="1" customWidth="1" min="78" max="78"/>
-    <col width="12.81640625" bestFit="1" customWidth="1" min="79" max="79"/>
-    <col width="22.7265625" bestFit="1" customWidth="1" min="80" max="80"/>
-    <col width="19.26953125" bestFit="1" customWidth="1" min="81" max="81"/>
-    <col width="21.54296875" bestFit="1" customWidth="1" min="82" max="82"/>
-    <col width="19" bestFit="1" customWidth="1" min="83" max="83"/>
-    <col width="25.7265625" bestFit="1" customWidth="1" min="84" max="84"/>
-    <col width="19.81640625" bestFit="1" customWidth="1" min="85" max="85"/>
-    <col width="15" bestFit="1" customWidth="1" min="86" max="86"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Report Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="T1" s="5">
-        <f>SUBTOTAL(9,T3:T1048576)</f>
-        <v/>
-      </c>
-      <c r="AL1" s="4">
-        <f>+AL3</f>
-        <v/>
-      </c>
-      <c r="AM1" s="4">
-        <f>+AM3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Previous Account</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Original Vendor</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Lender Account</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Lender Name</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Lender Ownership Pct</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Lender Funding Date</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Borrower Name</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Borrower Address</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Borrower City</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Borrower State</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Borrower Zip</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Work</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>Fax</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>Original Balance</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>Starting Balance</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>Current Balance</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>Note Rate</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>Investor Rate</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>Lien Position</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>Escrow Payment</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>Suspense Pmt.</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>Loan Charges</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>Unpaid Late Charges</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>Unpaid Interest</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>Sr.Loan Amount</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>Unearned Disc.</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr">
-        <is>
-          <t>Regular Payment</t>
-        </is>
-      </c>
-      <c r="AF2" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="AG2" s="2" t="inlineStr">
-        <is>
-          <t>Grace Days</t>
-        </is>
-      </c>
-      <c r="AH2" s="2" t="inlineStr">
-        <is>
-          <t>Minimum Late Charge</t>
-        </is>
-      </c>
-      <c r="AI2" s="2" t="inlineStr">
-        <is>
-          <t>Late Charge %</t>
-        </is>
-      </c>
-      <c r="AJ2" s="2" t="inlineStr">
-        <is>
-          <t>Paid To Date</t>
-        </is>
-      </c>
-      <c r="AK2" s="2" t="inlineStr">
-        <is>
-          <t>Boarding  Date</t>
-        </is>
-      </c>
-      <c r="AL2" s="2" t="inlineStr">
-        <is>
-          <t>Next Due Date</t>
-        </is>
-      </c>
-      <c r="AM2" s="2" t="inlineStr">
-        <is>
-          <t>Maturity Date</t>
-        </is>
-      </c>
-      <c r="AN2" s="2" t="inlineStr">
-        <is>
-          <t>Paid Off Date</t>
-        </is>
-      </c>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>Purchase Date</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr">
-        <is>
-          <t>Origination Date</t>
-        </is>
-      </c>
-      <c r="AQ2" s="2" t="inlineStr">
-        <is>
-          <t>Prop.Address</t>
-        </is>
-      </c>
-      <c r="AR2" s="2" t="inlineStr">
-        <is>
-          <t>Prop.City</t>
-        </is>
-      </c>
-      <c r="AS2" s="2" t="inlineStr">
-        <is>
-          <t>Prop.State</t>
-        </is>
-      </c>
-      <c r="AT2" s="2" t="inlineStr">
-        <is>
-          <t>Prop.Zip</t>
-        </is>
-      </c>
-      <c r="AU2" s="2" t="inlineStr">
-        <is>
-          <t>Appr.Value</t>
-        </is>
-      </c>
-      <c r="AV2" s="2" t="inlineStr">
-        <is>
-          <t>Appr.Source</t>
-        </is>
-      </c>
-      <c r="AW2" s="2" t="inlineStr">
-        <is>
-          <t>Appr.Date</t>
-        </is>
-      </c>
-      <c r="AX2" s="2" t="inlineStr">
-        <is>
-          <t>LTV</t>
-        </is>
-      </c>
-      <c r="AY2" s="2" t="inlineStr">
-        <is>
-          <t>Occupancy</t>
-        </is>
-      </c>
-      <c r="AZ2" s="2" t="inlineStr">
-        <is>
-          <t>Prop.Type</t>
-        </is>
-      </c>
-      <c r="BA2" s="2" t="inlineStr">
-        <is>
-          <t>ACH status</t>
-        </is>
-      </c>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>Rate Type</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>Deferred Principal Balance</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>Deferred Unpaid Interest</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>Deferred Unpaid Late Charges</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr">
-        <is>
-          <t>Deferred Unpaid Loan Charges</t>
-        </is>
-      </c>
-      <c r="BG2" s="2" t="inlineStr">
-        <is>
-          <t>Primary Purpose</t>
-        </is>
-      </c>
-      <c r="BH2" s="2" t="inlineStr">
-        <is>
-          <t>Invest Asset Number</t>
-        </is>
-      </c>
-      <c r="BI2" s="2" t="inlineStr">
-        <is>
-          <t>Days Late</t>
-        </is>
-      </c>
-      <c r="BJ2" s="2" t="inlineStr">
-        <is>
-          <t>Loan Type</t>
-        </is>
-      </c>
-      <c r="BK2" s="2" t="inlineStr">
-        <is>
-          <t>Draw Status</t>
-        </is>
-      </c>
-      <c r="BL2" s="2" t="inlineStr">
-        <is>
-          <t>Draw Close Date</t>
-        </is>
-      </c>
-      <c r="BM2" s="2" t="inlineStr">
-        <is>
-          <t>Maximum Draw</t>
-        </is>
-      </c>
-      <c r="BN2" s="2" t="inlineStr">
-        <is>
-          <t>Funded Amount</t>
-        </is>
-      </c>
-      <c r="BO2" s="2" t="inlineStr">
-        <is>
-          <t>Available Balance</t>
-        </is>
-      </c>
-      <c r="BP2" s="2" t="inlineStr">
-        <is>
-          <t>Borrower Full Name</t>
-        </is>
-      </c>
-      <c r="BQ2" s="2" t="inlineStr">
-        <is>
-          <t>CoBorrower</t>
-        </is>
-      </c>
-      <c r="BR2" s="2" t="inlineStr">
-        <is>
-          <t>Restricted Balance</t>
-        </is>
-      </c>
-      <c r="BS2" s="2" t="inlineStr">
-        <is>
-          <t>Default Interest Rate</t>
-        </is>
-      </c>
-      <c r="BT2" s="2" t="inlineStr">
-        <is>
-          <t>Closed Date</t>
-        </is>
-      </c>
-      <c r="BU2" s="2" t="inlineStr">
-        <is>
-          <t>Closed Reason</t>
-        </is>
-      </c>
-      <c r="BV2" s="2" t="inlineStr">
-        <is>
-          <t>Default Interest Active Status</t>
-        </is>
-      </c>
-      <c r="BW2" s="2" t="inlineStr">
-        <is>
-          <t>Escrow Balance</t>
-        </is>
-      </c>
-      <c r="BX2" s="2" t="inlineStr">
-        <is>
-          <t>Reserve Balance</t>
-        </is>
-      </c>
-      <c r="BY2" s="2" t="inlineStr">
-        <is>
-          <t>Borrower Email</t>
-        </is>
-      </c>
-      <c r="BZ2" s="2" t="inlineStr">
-        <is>
-          <t>Sec Financing</t>
-        </is>
-      </c>
-      <c r="CA2" s="2" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="CB2" s="2" t="inlineStr">
-        <is>
-          <t>Originator Loan Number</t>
-        </is>
-      </c>
-      <c r="CC2" s="2" t="inlineStr">
-        <is>
-          <t>Borrower First Name</t>
-        </is>
-      </c>
-      <c r="CD2" s="2" t="inlineStr">
-        <is>
-          <t>Borrower Middle Name</t>
-        </is>
-      </c>
-      <c r="CE2" s="2" t="inlineStr">
-        <is>
-          <t>Borrower Last Name</t>
-        </is>
-      </c>
-      <c r="CF2" s="2" t="inlineStr">
-        <is>
-          <t>Prepayment Expiration Date</t>
-        </is>
-      </c>
-      <c r="CG2" s="2" t="inlineStr">
-        <is>
-          <t>Default Int Is Enabled</t>
-        </is>
-      </c>
-      <c r="CH2" s="2" t="inlineStr">
-        <is>
-          <t>Other Payments</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>399147585</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>FCI</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>04461</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>5ARCHASSET</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>14733</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Pacific Life Insurance Company (Corevest)</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>100.000%</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>42887</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>R&amp;M Commercial Real Estate, LLC
-Ron Jackson</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>335 Fields Drive</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>28315</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>(910)944-7453</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>(317)710-0126</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>(910)691-5907;(910)215-3841</t>
-        </is>
-      </c>
-      <c r="R3" s="5" t="n">
-        <v>653300</v>
-      </c>
-      <c r="S3" s="5" t="n">
-        <v>653300</v>
-      </c>
-      <c r="T3" s="5" t="n">
-        <v>558948.25</v>
-      </c>
-      <c r="U3" s="6" t="inlineStr">
-        <is>
-          <t>6.25000%</t>
-        </is>
-      </c>
-      <c r="V3" s="6" t="inlineStr">
-        <is>
-          <t>6.00000%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="X3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA3" s="5" t="n">
-        <v>402.25</v>
-      </c>
-      <c r="AB3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="5" t="n">
-        <v>4022.48</v>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>Performing</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="3" t="inlineStr">
-        <is>
-          <t>10.000%</t>
-        </is>
-      </c>
-      <c r="AJ3" s="4" t="n">
-        <v>46174</v>
-      </c>
-      <c r="AK3" s="4" t="n">
-        <v>42831</v>
-      </c>
-      <c r="AL3" s="4" t="n">
-        <v>46204</v>
-      </c>
-      <c r="AM3" s="4" t="n">
-        <v>46478</v>
-      </c>
-      <c r="AP3" s="4" t="n">
-        <v>42825</v>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>5 Vail Place</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>Pinehurst</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>28374</t>
-        </is>
-      </c>
-      <c r="AU3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" s="3" t="inlineStr">
-        <is>
-          <t>31.130%</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Vacant</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>Residential Income 1-4</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>Fixed Rate</t>
-        </is>
-      </c>
-      <c r="BC3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>Business</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>04461</t>
-        </is>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>Business Purpose Loan</t>
-        </is>
-      </c>
-      <c r="BM3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" s="5" t="n">
-        <v>558948.25</v>
-      </c>
-      <c r="BO3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>R&amp;M Commercial Real Estate, LLCRon Jackson</t>
-        </is>
-      </c>
-      <c r="BR3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BW3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>qualitybuilt1@hotmail.com</t>
-        </is>
-      </c>
-      <c r="CA3" s="4" t="n">
-        <v>42831.46254070602</v>
-      </c>
-      <c r="CG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="CH3" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
